--- a/artfynd/A 54724-2022 artfynd.xlsx
+++ b/artfynd/A 54724-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120021809</v>
+        <v>120021720</v>
       </c>
       <c r="B2" t="n">
-        <v>101249</v>
+        <v>108787</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,17 +715,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Uddberga 400m NV, Srm</t>
+          <t>Uddberga 450m NV, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609789</v>
+        <v>609829</v>
       </c>
       <c r="R2" t="n">
-        <v>6544492</v>
+        <v>6544574</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,9 +767,9 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägren grusväg</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120021720</v>
+        <v>120021809</v>
       </c>
       <c r="B3" t="n">
-        <v>108787</v>
+        <v>101249</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>221317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,17 +827,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Uddberga 450m NV, Srm</t>
+          <t>Uddberga 400m NV, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609829</v>
+        <v>609789</v>
       </c>
       <c r="R3" t="n">
-        <v>6544574</v>
+        <v>6544492</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,9 +879,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägren grusväg</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 54724-2022 artfynd.xlsx
+++ b/artfynd/A 54724-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120021720</v>
+        <v>120021809</v>
       </c>
       <c r="B2" t="n">
-        <v>108787</v>
+        <v>101249</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>221317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,17 +715,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Uddberga 450m NV, Srm</t>
+          <t>Uddberga 400m NV, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609829</v>
+        <v>609789</v>
       </c>
       <c r="R2" t="n">
-        <v>6544574</v>
+        <v>6544492</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,9 +767,9 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Vägren grusväg</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120021809</v>
+        <v>120021720</v>
       </c>
       <c r="B3" t="n">
-        <v>101249</v>
+        <v>108787</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,17 +827,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Uddberga 400m NV, Srm</t>
+          <t>Uddberga 450m NV, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609789</v>
+        <v>609829</v>
       </c>
       <c r="R3" t="n">
-        <v>6544492</v>
+        <v>6544574</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,9 +879,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Vägren grusväg</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 54724-2022 artfynd.xlsx
+++ b/artfynd/A 54724-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120021720</v>
+        <v>120021809</v>
       </c>
       <c r="B2" t="n">
-        <v>108787</v>
+        <v>101272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>221317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,17 +715,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Uddberga 450m NV, Srm</t>
+          <t>Uddberga 400m NV, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609829</v>
+        <v>609789</v>
       </c>
       <c r="R2" t="n">
-        <v>6544574</v>
+        <v>6544492</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,9 +767,9 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Vägren grusväg</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120021809</v>
+        <v>120021720</v>
       </c>
       <c r="B3" t="n">
-        <v>101249</v>
+        <v>108811</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,17 +827,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Uddberga 400m NV, Srm</t>
+          <t>Uddberga 450m NV, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609789</v>
+        <v>609829</v>
       </c>
       <c r="R3" t="n">
-        <v>6544492</v>
+        <v>6544574</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,9 +879,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Vägren grusväg</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 54724-2022 artfynd.xlsx
+++ b/artfynd/A 54724-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120021809</v>
+        <v>120021720</v>
       </c>
       <c r="B2" t="n">
-        <v>101272</v>
+        <v>108811</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,17 +715,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Uddberga 400m NV, Srm</t>
+          <t>Uddberga 450m NV, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609789</v>
+        <v>609829</v>
       </c>
       <c r="R2" t="n">
-        <v>6544492</v>
+        <v>6544574</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,9 +767,9 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägren grusväg</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120021720</v>
+        <v>120021809</v>
       </c>
       <c r="B3" t="n">
-        <v>108811</v>
+        <v>101272</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>221317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,17 +827,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Uddberga 450m NV, Srm</t>
+          <t>Uddberga 400m NV, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609829</v>
+        <v>609789</v>
       </c>
       <c r="R3" t="n">
-        <v>6544574</v>
+        <v>6544492</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,9 +879,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägren grusväg</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 54724-2022 artfynd.xlsx
+++ b/artfynd/A 54724-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120021720</v>
+        <v>120021809</v>
       </c>
       <c r="B2" t="n">
-        <v>108811</v>
+        <v>101272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>221317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Gullklöver</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Trifolium aureum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Pollich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,17 +715,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Uddberga 450m NV, Srm</t>
+          <t>Uddberga 400m NV, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609829</v>
+        <v>609789</v>
       </c>
       <c r="R2" t="n">
-        <v>6544574</v>
+        <v>6544492</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,9 +767,9 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Vägren grusväg</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120021809</v>
+        <v>120021720</v>
       </c>
       <c r="B3" t="n">
-        <v>101272</v>
+        <v>108811</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221317</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,17 +827,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Uddberga 400m NV, Srm</t>
+          <t>Uddberga 450m NV, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609789</v>
+        <v>609829</v>
       </c>
       <c r="R3" t="n">
-        <v>6544492</v>
+        <v>6544574</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,9 +879,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Vägren grusväg</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 54724-2022 artfynd.xlsx
+++ b/artfynd/A 54724-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,118 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125555431</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102771</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Uddberga NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>610069</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6544600</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Lövskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54724-2022 artfynd.xlsx
+++ b/artfynd/A 54724-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>125555431</v>
       </c>
       <c r="B4" t="n">
-        <v>102826</v>
+        <v>102833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54724-2022 artfynd.xlsx
+++ b/artfynd/A 54724-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>125555431</v>
       </c>
       <c r="B4" t="n">
-        <v>102833</v>
+        <v>102836</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54724-2022 artfynd.xlsx
+++ b/artfynd/A 54724-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>125555431</v>
       </c>
       <c r="B4" t="n">
-        <v>102836</v>
+        <v>102840</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54724-2022 artfynd.xlsx
+++ b/artfynd/A 54724-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>125555431</v>
       </c>
       <c r="B4" t="n">
-        <v>102840</v>
+        <v>102841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54724-2022 artfynd.xlsx
+++ b/artfynd/A 54724-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>125555431</v>
       </c>
       <c r="B4" t="n">
-        <v>102841</v>
+        <v>102843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54724-2022 artfynd.xlsx
+++ b/artfynd/A 54724-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>125555431</v>
       </c>
       <c r="B4" t="n">
-        <v>102843</v>
+        <v>102845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54724-2022 artfynd.xlsx
+++ b/artfynd/A 54724-2022 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>125555431</v>
       </c>
       <c r="B4" t="n">
-        <v>102845</v>
+        <v>102849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
